--- a/data/maestro/Maestro_UPS_v2.xlsx
+++ b/data/maestro/Maestro_UPS_v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grpleg-my.sharepoint.com/personal/alvaro_zegarra_legrand_com/Documents/PROYECTO_PM/veritrade_clasificador_ups/data/maestro/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="11_CDF1C2B03EDA0A11C255FBE40C2039B7CF1AFE10" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9AE8FA4-C3DC-4A2A-B01A-DC7BE1213E3A}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="11_CDF1C2B03EDA0A11C255FBE40C2039B7CF1AFE10" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF04D854-2395-4FF5-99D4-0D3AC10D86BC}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0_Instrucciones" sheetId="1" r:id="rId1"/>
@@ -19,8 +19,8 @@
     <sheet name="1b_Palabras_Ignorar" sheetId="4" state="hidden" r:id="rId4"/>
     <sheet name="1c_Marca_Por_Defecto" sheetId="5" r:id="rId5"/>
     <sheet name="2_Caracteristicas" sheetId="6" r:id="rId6"/>
-    <sheet name="3_Tecnico_Potencia_NOEDIT" sheetId="7" r:id="rId7"/>
-    <sheet name="4_Tecnico_RegexMarca_NOEDIT" sheetId="8" r:id="rId8"/>
+    <sheet name="3_Tecnico_Potencia_NOEDIT" sheetId="7" state="hidden" r:id="rId7"/>
+    <sheet name="4_Tecnico_RegexMarca_NOEDIT" sheetId="8" state="hidden" r:id="rId8"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -1607,7 +1607,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1654,7 +1654,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1676,8 +1676,14 @@
         <fgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -1796,11 +1802,125 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1831,9 +1951,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1872,12 +1989,394 @@
     <xf numFmtId="20" fontId="3" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="31">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFC6E0B4"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFBFBFBF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFBFBFBF"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFBFBFBF"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FFBFBFBF"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFBFBFBF"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FFBFBFBF"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFBFBFBF"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFBFBFBF"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FFBFBFBF"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FFBFBFBF"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFBFBFBF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFBFBFBF"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFBFBFBF"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFBFBFBF"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+      </font>
+      <alignment horizontal="general" vertical="center"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+      </font>
+      <alignment horizontal="general" vertical="center"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+      </font>
+      <alignment horizontal="general" vertical="center"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+        <horizontal style="thin">
+          <color auto="1"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFC6E0B4"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -2100,92 +2599,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-      </font>
-      <alignment horizontal="general" vertical="center"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFBFBFBF"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FFBFBFBF"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFBFBFBF"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-      </font>
-      <alignment horizontal="general" vertical="center"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFBFBFBF"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFBFBFBF"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFBFBFBF"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFBFBFBF"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-      </font>
-      <alignment horizontal="general" vertical="center"/>
-      <border>
-        <left/>
-        <right style="thin">
-          <color rgb="FFBFBFBF"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFBFBFBF"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFBFBFBF"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
       <border outline="0">
         <top style="thin">
           <color rgb="FFBFBFBF"/>
@@ -2247,7 +2660,12 @@
       </border>
     </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleLight1 2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="TableStyleLight1 2" pivot="0" count="2" xr9:uid="{47937CA9-E4E9-4EB3-86E5-9529306AECC0}">
+      <tableStyleElement type="wholeTable" dxfId="9"/>
+      <tableStyleElement type="headerRow" dxfId="10"/>
+    </tableStyle>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2260,26 +2678,54 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:C73" totalsRowShown="0" headerRowDxfId="16" headerRowBorderDxfId="15" tableBorderDxfId="14" totalsRowBorderDxfId="13">
-  <autoFilter ref="A1:C73" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Patron_Busqueda" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Marca_Estandar" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Prioridad" dataDxfId="10"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{1879BB27-7700-4B33-A850-7BCE8FDEB2D3}" name="Table3" displayName="Table3" ref="A1:B4" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="15" tableBorderDxfId="16" totalsRowBorderDxfId="14">
+  <autoFilter ref="A1:B4" xr:uid="{1879BB27-7700-4B33-A850-7BCE8FDEB2D3}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{7B5D0F09-2B49-423E-B6FF-7C3F7776B95F}" name="Parametro" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{EC034524-0683-4FA3-9330-E2AE7E481D5D}" name="Valor" dataDxfId="12"/>
   </tableColumns>
-  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1 2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table2" displayName="Table2" ref="A1:E275" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6" totalsRowBorderDxfId="5">
-  <autoFilter ref="A1:E275" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:C73" totalsRowShown="0" headerRowDxfId="30" headerRowBorderDxfId="29" tableBorderDxfId="28" totalsRowBorderDxfId="27">
+  <autoFilter ref="A1:C73" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Patron_Busqueda" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Marca_Estandar" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Prioridad" dataDxfId="6"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1 2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{57B48D49-2642-4E65-8D36-F6E5C8803046}" name="Table4" displayName="Table4" ref="A1:B3" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="4" tableBorderDxfId="5" totalsRowBorderDxfId="3">
+  <autoFilter ref="A1:B3" xr:uid="{57B48D49-2642-4E65-8D36-F6E5C8803046}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{5EC98273-43AA-4C61-A35B-DCF3648C143A}" name="Es_Producto_Principal" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{D85189CC-1C53-4946-952A-604C6F638CEA}" name="Marca_Default" dataDxfId="1"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1 2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table2" displayName="Table2" ref="A1:E275" totalsRowShown="0" headerRowDxfId="26" dataDxfId="24" headerRowBorderDxfId="25" tableBorderDxfId="23" totalsRowBorderDxfId="22">
+  <autoFilter ref="A1:E275" xr:uid="{00000000-0009-0000-0100-000002000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Salida_Fases"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Variable" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Valor_Resultado" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Palabra_Clave" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Prioridad" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Comentario" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Variable" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Valor_Resultado" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Palabra_Clave" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Prioridad" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Comentario" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2707,34 +3153,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="29" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="27" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="27" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="31" t="s">
         <v>31</v>
       </c>
     </row>
@@ -2743,6 +3189,9 @@
   <headerFooter>
     <oddHeader>&amp;L&amp;"Aptos"&amp;11&amp;K000000 Internal&amp;1#_x000D_</oddHeader>
   </headerFooter>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -2757,805 +3206,805 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="34" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="C3" s="12">
+      <c r="C3" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="12">
+      <c r="C12" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="C17" s="12">
+      <c r="C17" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="C19" s="12">
+      <c r="C19" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="35" t="s">
         <v>53</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="35" t="s">
         <v>53</v>
       </c>
-      <c r="C20" s="12">
+      <c r="C20" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="11" t="s">
+      <c r="A21" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="C21" s="12">
+      <c r="C21" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="11" t="s">
+      <c r="A22" s="35" t="s">
         <v>55</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="35" t="s">
         <v>55</v>
       </c>
-      <c r="C22" s="12">
+      <c r="C22" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="11" t="s">
+      <c r="A23" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="35" t="s">
         <v>57</v>
       </c>
-      <c r="C23" s="12">
+      <c r="C23" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="11" t="s">
+      <c r="A24" s="35" t="s">
         <v>58</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="35" t="s">
         <v>58</v>
       </c>
-      <c r="C24" s="12">
+      <c r="C24" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="11" t="s">
+      <c r="A25" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="C25" s="12">
+      <c r="C25" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="11" t="s">
+      <c r="A26" s="35" t="s">
         <v>60</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="35" t="s">
         <v>60</v>
       </c>
-      <c r="C26" s="12">
+      <c r="C26" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="11" t="s">
+      <c r="A27" s="35" t="s">
         <v>61</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="35" t="s">
         <v>61</v>
       </c>
-      <c r="C27" s="12">
+      <c r="C27" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="11" t="s">
+      <c r="A28" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="C28" s="12">
+      <c r="C28" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="11" t="s">
+      <c r="A29" s="35" t="s">
         <v>63</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="B29" s="35" t="s">
         <v>63</v>
       </c>
-      <c r="C29" s="12">
+      <c r="C29" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="11" t="s">
+      <c r="A30" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="B30" s="35" t="s">
         <v>65</v>
       </c>
-      <c r="C30" s="12">
+      <c r="C30" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="11" t="s">
+      <c r="A31" s="35" t="s">
         <v>65</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="35" t="s">
         <v>65</v>
       </c>
-      <c r="C31" s="12">
+      <c r="C31" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="11" t="s">
+      <c r="A32" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="B32" s="35" t="s">
         <v>67</v>
       </c>
-      <c r="C32" s="12">
+      <c r="C32" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="11" t="s">
+      <c r="A33" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="B33" s="8" t="s">
+      <c r="B33" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="C33" s="12">
+      <c r="C33" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" s="11" t="s">
+      <c r="A34" s="35" t="s">
         <v>69</v>
       </c>
-      <c r="B34" s="8" t="s">
+      <c r="B34" s="35" t="s">
         <v>69</v>
       </c>
-      <c r="C34" s="12">
+      <c r="C34" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" s="11" t="s">
+      <c r="A35" s="35" t="s">
         <v>70</v>
       </c>
-      <c r="B35" s="8" t="s">
+      <c r="B35" s="35" t="s">
         <v>70</v>
       </c>
-      <c r="C35" s="12">
+      <c r="C35" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" s="11" t="s">
+      <c r="A36" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="B36" s="8" t="s">
+      <c r="B36" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="C36" s="12">
+      <c r="C36" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" s="11" t="s">
+      <c r="A37" s="35" t="s">
         <v>73</v>
       </c>
-      <c r="B37" s="8" t="s">
+      <c r="B37" s="35" t="s">
         <v>73</v>
       </c>
-      <c r="C37" s="12">
+      <c r="C37" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" s="11" t="s">
+      <c r="A38" s="35" t="s">
         <v>74</v>
       </c>
-      <c r="B38" s="8" t="s">
+      <c r="B38" s="35" t="s">
         <v>74</v>
       </c>
-      <c r="C38" s="12">
+      <c r="C38" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" s="11" t="s">
+      <c r="A39" s="35" t="s">
         <v>75</v>
       </c>
-      <c r="B39" s="8" t="s">
+      <c r="B39" s="35" t="s">
         <v>75</v>
       </c>
-      <c r="C39" s="12">
+      <c r="C39" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" s="11" t="s">
+      <c r="A40" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="B40" s="8" t="s">
+      <c r="B40" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="C40" s="12">
+      <c r="C40" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" s="11" t="s">
+      <c r="A41" s="35" t="s">
         <v>77</v>
       </c>
-      <c r="B41" s="8" t="s">
+      <c r="B41" s="35" t="s">
         <v>78</v>
       </c>
-      <c r="C41" s="12">
+      <c r="C41" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" s="11" t="s">
+      <c r="A42" s="35" t="s">
         <v>79</v>
       </c>
-      <c r="B42" s="8" t="s">
+      <c r="B42" s="35" t="s">
         <v>78</v>
       </c>
-      <c r="C42" s="12">
+      <c r="C42" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" s="11" t="s">
+      <c r="A43" s="35" t="s">
         <v>80</v>
       </c>
-      <c r="B43" s="8" t="s">
+      <c r="B43" s="35" t="s">
         <v>80</v>
       </c>
-      <c r="C43" s="12">
+      <c r="C43" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" s="11" t="s">
+      <c r="A44" s="35" t="s">
         <v>81</v>
       </c>
-      <c r="B44" s="8" t="s">
+      <c r="B44" s="35" t="s">
         <v>81</v>
       </c>
-      <c r="C44" s="12">
+      <c r="C44" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" s="11" t="s">
+      <c r="A45" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="B45" s="8" t="s">
+      <c r="B45" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="C45" s="12">
+      <c r="C45" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" s="11" t="s">
+      <c r="A46" s="35" t="s">
         <v>83</v>
       </c>
-      <c r="B46" s="8" t="s">
+      <c r="B46" s="35" t="s">
         <v>83</v>
       </c>
-      <c r="C46" s="12">
+      <c r="C46" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" s="11" t="s">
+      <c r="A47" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="B47" s="8" t="s">
+      <c r="B47" s="35" t="s">
         <v>83</v>
       </c>
-      <c r="C47" s="12">
+      <c r="C47" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48" s="11" t="s">
+      <c r="A48" s="35" t="s">
         <v>85</v>
       </c>
-      <c r="B48" s="8" t="s">
+      <c r="B48" s="35" t="s">
         <v>85</v>
       </c>
-      <c r="C48" s="12">
+      <c r="C48" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" s="11" t="s">
+      <c r="A49" s="35" t="s">
         <v>86</v>
       </c>
-      <c r="B49" s="8" t="s">
+      <c r="B49" s="35" t="s">
         <v>86</v>
       </c>
-      <c r="C49" s="12">
+      <c r="C49" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" s="11" t="s">
+      <c r="A50" s="35" t="s">
         <v>87</v>
       </c>
-      <c r="B50" s="8" t="s">
+      <c r="B50" s="35" t="s">
         <v>87</v>
       </c>
-      <c r="C50" s="12">
+      <c r="C50" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" s="11" t="s">
+      <c r="A51" s="35" t="s">
         <v>88</v>
       </c>
-      <c r="B51" s="8" t="s">
+      <c r="B51" s="35" t="s">
         <v>87</v>
       </c>
-      <c r="C51" s="12">
+      <c r="C51" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" s="11" t="s">
+      <c r="A52" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="B52" s="8" t="s">
+      <c r="B52" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="C52" s="12">
+      <c r="C52" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" s="11" t="s">
+      <c r="A53" s="35" t="s">
         <v>90</v>
       </c>
-      <c r="B53" s="8" t="s">
+      <c r="B53" s="35" t="s">
         <v>90</v>
       </c>
-      <c r="C53" s="12">
+      <c r="C53" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" s="11" t="s">
+      <c r="A54" s="35" t="s">
         <v>91</v>
       </c>
-      <c r="B54" s="8" t="s">
+      <c r="B54" s="35" t="s">
         <v>91</v>
       </c>
-      <c r="C54" s="12">
+      <c r="C54" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55" s="11" t="s">
+      <c r="A55" s="35" t="s">
         <v>92</v>
       </c>
-      <c r="B55" s="8" t="s">
+      <c r="B55" s="35" t="s">
         <v>92</v>
       </c>
-      <c r="C55" s="12">
+      <c r="C55" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" s="11" t="s">
+      <c r="A56" s="35" t="s">
         <v>93</v>
       </c>
-      <c r="B56" s="8" t="s">
+      <c r="B56" s="35" t="s">
         <v>93</v>
       </c>
-      <c r="C56" s="12">
+      <c r="C56" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" s="11" t="s">
+      <c r="A57" s="35" t="s">
         <v>94</v>
       </c>
-      <c r="B57" s="8" t="s">
+      <c r="B57" s="35" t="s">
         <v>94</v>
       </c>
-      <c r="C57" s="12">
+      <c r="C57" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" s="11" t="s">
+      <c r="A58" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="B58" s="8" t="s">
+      <c r="B58" s="35" t="s">
         <v>94</v>
       </c>
-      <c r="C58" s="12">
+      <c r="C58" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A59" s="11" t="s">
+      <c r="A59" s="35" t="s">
         <v>96</v>
       </c>
-      <c r="B59" s="8" t="s">
+      <c r="B59" s="35" t="s">
         <v>96</v>
       </c>
-      <c r="C59" s="12">
+      <c r="C59" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60" s="11" t="s">
+      <c r="A60" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="B60" s="8" t="s">
+      <c r="B60" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="C60" s="12">
+      <c r="C60" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A61" s="11" t="s">
+      <c r="A61" s="35" t="s">
         <v>98</v>
       </c>
-      <c r="B61" s="8" t="s">
+      <c r="B61" s="35" t="s">
         <v>98</v>
       </c>
-      <c r="C61" s="12">
+      <c r="C61" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62" s="11" t="s">
+      <c r="A62" s="35" t="s">
         <v>99</v>
       </c>
-      <c r="B62" s="8" t="s">
+      <c r="B62" s="35" t="s">
         <v>99</v>
       </c>
-      <c r="C62" s="12">
+      <c r="C62" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63" s="11" t="s">
+      <c r="A63" s="35" t="s">
         <v>100</v>
       </c>
-      <c r="B63" s="8" t="s">
+      <c r="B63" s="35" t="s">
         <v>100</v>
       </c>
-      <c r="C63" s="12">
+      <c r="C63" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64" s="11" t="s">
+      <c r="A64" s="35" t="s">
         <v>101</v>
       </c>
-      <c r="B64" s="8" t="s">
+      <c r="B64" s="35" t="s">
         <v>101</v>
       </c>
-      <c r="C64" s="12">
+      <c r="C64" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A65" s="11" t="s">
+      <c r="A65" s="35" t="s">
         <v>102</v>
       </c>
-      <c r="B65" s="8" t="s">
+      <c r="B65" s="35" t="s">
         <v>102</v>
       </c>
-      <c r="C65" s="12">
+      <c r="C65" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A66" s="11" t="s">
+      <c r="A66" s="35" t="s">
         <v>103</v>
       </c>
-      <c r="B66" s="8" t="s">
+      <c r="B66" s="35" t="s">
         <v>103</v>
       </c>
-      <c r="C66" s="12">
+      <c r="C66" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A67" s="11" t="s">
+      <c r="A67" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="B67" s="8" t="s">
+      <c r="B67" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="C67" s="12">
+      <c r="C67" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A68" s="11" t="s">
+      <c r="A68" s="35" t="s">
         <v>105</v>
       </c>
-      <c r="B68" s="8" t="s">
+      <c r="B68" s="35" t="s">
         <v>105</v>
       </c>
-      <c r="C68" s="12">
+      <c r="C68" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A69" s="11" t="s">
+      <c r="A69" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="B69" s="8" t="s">
+      <c r="B69" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="C69" s="12">
+      <c r="C69" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A70" s="11" t="s">
+      <c r="A70" s="35" t="s">
         <v>107</v>
       </c>
-      <c r="B70" s="8" t="s">
+      <c r="B70" s="35" t="s">
         <v>107</v>
       </c>
-      <c r="C70" s="12">
+      <c r="C70" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A71" s="11" t="s">
+      <c r="A71" s="35" t="s">
         <v>108</v>
       </c>
-      <c r="B71" s="8" t="s">
+      <c r="B71" s="35" t="s">
         <v>108</v>
       </c>
-      <c r="C71" s="12">
+      <c r="C71" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A72" s="11" t="s">
+      <c r="A72" s="35" t="s">
         <v>109</v>
       </c>
-      <c r="B72" s="8" t="s">
+      <c r="B72" s="35" t="s">
         <v>109</v>
       </c>
-      <c r="C72" s="12">
+      <c r="C72" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A73" s="16" t="s">
+      <c r="A73" s="35" t="s">
         <v>110</v>
       </c>
-      <c r="B73" s="17" t="s">
+      <c r="B73" s="35" t="s">
         <v>110</v>
       </c>
-      <c r="C73" s="18">
+      <c r="C73" s="35">
         <v>1</v>
       </c>
     </row>
@@ -3768,31 +4217,31 @@
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="1" max="1" width="21.6640625" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="B2" s="8" t="s">
+      <c r="A2" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="B2" s="12" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="b">
+      <c r="A3" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="17" t="s">
         <v>3</v>
       </c>
     </row>
@@ -3801,6 +4250,9 @@
   <headerFooter>
     <oddHeader>&amp;L&amp;"Aptos"&amp;11&amp;K000000 Internal&amp;1#_x000D_&amp;"Calibri"&amp;11&amp;K000000&amp;"Aptos"&amp;1 &amp;K000000 Internal#_x000D_</oddHeader>
   </headerFooter>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -3817,23 +4269,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="20" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
         <v>141</v>
       </c>
@@ -3850,7 +4302,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
         <v>141</v>
       </c>
@@ -3867,7 +4319,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
         <v>141</v>
       </c>
@@ -3884,7 +4336,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
         <v>141</v>
       </c>
@@ -3901,7 +4353,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>141</v>
       </c>
@@ -3918,7 +4370,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>141</v>
       </c>
@@ -3935,7 +4387,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>141</v>
       </c>
@@ -3952,7 +4404,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>141</v>
       </c>
@@ -3969,7 +4421,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
         <v>141</v>
       </c>
@@ -3986,7 +4438,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>141</v>
       </c>
@@ -4003,7 +4455,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>141</v>
       </c>
@@ -4020,7 +4472,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>141</v>
       </c>
@@ -4037,7 +4489,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
         <v>141</v>
       </c>
@@ -4054,7 +4506,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>29</v>
       </c>
@@ -4071,7 +4523,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
         <v>29</v>
       </c>
@@ -4088,7 +4540,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>29</v>
       </c>
@@ -4105,7 +4557,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>29</v>
       </c>
@@ -4122,7 +4574,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>29</v>
       </c>
@@ -4139,7 +4591,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
         <v>29</v>
       </c>
@@ -4156,7 +4608,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>29</v>
       </c>
@@ -4173,7 +4625,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
         <v>29</v>
       </c>
@@ -4190,7 +4642,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>29</v>
       </c>
@@ -4207,7 +4659,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
         <v>29</v>
       </c>
@@ -4224,7 +4676,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
         <v>29</v>
       </c>
@@ -4241,7 +4693,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
         <v>29</v>
       </c>
@@ -4258,7 +4710,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
         <v>29</v>
       </c>
@@ -4275,7 +4727,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="11" t="s">
         <v>29</v>
       </c>
@@ -4292,7 +4744,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="11" t="s">
         <v>29</v>
       </c>
@@ -4309,7 +4761,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
         <v>29</v>
       </c>
@@ -4326,7 +4778,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="11" t="s">
         <v>29</v>
       </c>
@@ -4343,7 +4795,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="11" t="s">
         <v>29</v>
       </c>
@@ -4360,7 +4812,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="11" t="s">
         <v>29</v>
       </c>
@@ -4377,7 +4829,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="11" t="s">
         <v>29</v>
       </c>
@@ -4394,7 +4846,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="11" t="s">
         <v>29</v>
       </c>
@@ -4411,7 +4863,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="11" t="s">
         <v>29</v>
       </c>
@@ -4428,7 +4880,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="11" t="s">
         <v>29</v>
       </c>
@@ -4445,7 +4897,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="11" t="s">
         <v>29</v>
       </c>
@@ -4462,7 +4914,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="11" t="s">
         <v>29</v>
       </c>
@@ -4479,7 +4931,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="11" t="s">
         <v>29</v>
       </c>
@@ -4496,7 +4948,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="11" t="s">
         <v>29</v>
       </c>
@@ -4513,7 +4965,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="11" t="s">
         <v>29</v>
       </c>
@@ -4530,7 +4982,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="11" t="s">
         <v>29</v>
       </c>
@@ -4547,7 +4999,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="11" t="s">
         <v>29</v>
       </c>
@@ -4564,7 +5016,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="11" t="s">
         <v>29</v>
       </c>
@@ -4581,7 +5033,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="11" t="s">
         <v>29</v>
       </c>
@@ -4598,7 +5050,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="11" t="s">
         <v>29</v>
       </c>
@@ -4615,7 +5067,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="11" t="s">
         <v>29</v>
       </c>
@@ -4632,7 +5084,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="11" t="s">
         <v>29</v>
       </c>
@@ -4649,7 +5101,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="11" t="s">
         <v>29</v>
       </c>
@@ -4666,7 +5118,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="11" t="s">
         <v>29</v>
       </c>
@@ -4683,7 +5135,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="11" t="s">
         <v>29</v>
       </c>
@@ -4700,7 +5152,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="11" t="s">
         <v>29</v>
       </c>
@@ -4717,7 +5169,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="11" t="s">
         <v>29</v>
       </c>
@@ -4734,1856 +5186,1856 @@
         <v>200</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A55" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B55" s="23" t="s">
+    <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B55" s="22" t="s">
         <v>198</v>
       </c>
-      <c r="C55" s="23" t="s">
+      <c r="C55" s="22" t="s">
         <v>208</v>
       </c>
-      <c r="D55" s="23">
+      <c r="D55" s="22">
         <v>3</v>
       </c>
-      <c r="E55" s="24" t="s">
+      <c r="E55" s="23" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A56" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B56" s="23" t="s">
+    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B56" s="22" t="s">
         <v>198</v>
       </c>
-      <c r="C56" s="23" t="s">
+      <c r="C56" s="22" t="s">
         <v>209</v>
       </c>
-      <c r="D56" s="23">
+      <c r="D56" s="22">
         <v>3</v>
       </c>
-      <c r="E56" s="24" t="s">
+      <c r="E56" s="23" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A57" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B57" s="23" t="s">
+    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B57" s="22" t="s">
         <v>198</v>
       </c>
-      <c r="C57" s="23" t="s">
+      <c r="C57" s="22" t="s">
         <v>210</v>
       </c>
-      <c r="D57" s="23">
+      <c r="D57" s="22">
         <v>3</v>
       </c>
-      <c r="E57" s="24" t="s">
+      <c r="E57" s="23" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A58" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B58" s="23" t="s">
+    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B58" s="22" t="s">
         <v>198</v>
       </c>
-      <c r="C58" s="23" t="s">
+      <c r="C58" s="22" t="s">
         <v>211</v>
       </c>
-      <c r="D58" s="23">
+      <c r="D58" s="22">
         <v>3</v>
       </c>
-      <c r="E58" s="24" t="s">
+      <c r="E58" s="23" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A59" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B59" s="23" t="s">
+    <row r="59" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B59" s="22" t="s">
         <v>198</v>
       </c>
-      <c r="C59" s="23" t="s">
+      <c r="C59" s="22" t="s">
         <v>212</v>
       </c>
-      <c r="D59" s="23">
+      <c r="D59" s="22">
         <v>3</v>
       </c>
-      <c r="E59" s="24" t="s">
+      <c r="E59" s="23" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A60" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B60" s="23" t="s">
+    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B60" s="22" t="s">
         <v>198</v>
       </c>
-      <c r="C60" s="23" t="s">
+      <c r="C60" s="22" t="s">
         <v>213</v>
       </c>
-      <c r="D60" s="23">
+      <c r="D60" s="22">
         <v>3</v>
       </c>
-      <c r="E60" s="24" t="s">
+      <c r="E60" s="23" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A61" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B61" s="23" t="s">
+    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B61" s="22" t="s">
         <v>198</v>
       </c>
-      <c r="C61" s="23" t="s">
+      <c r="C61" s="22" t="s">
         <v>214</v>
       </c>
-      <c r="D61" s="23">
+      <c r="D61" s="22">
         <v>3</v>
       </c>
-      <c r="E61" s="24" t="s">
+      <c r="E61" s="23" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A62" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B62" s="23" t="s">
+    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B62" s="22" t="s">
         <v>215</v>
       </c>
-      <c r="C62" s="23" t="s">
+      <c r="C62" s="22" t="s">
         <v>216</v>
       </c>
-      <c r="D62" s="23">
+      <c r="D62" s="22">
         <v>4</v>
       </c>
-      <c r="E62" s="24" t="s">
+      <c r="E62" s="23" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A63" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B63" s="23" t="s">
+    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B63" s="22" t="s">
         <v>215</v>
       </c>
-      <c r="C63" s="23" t="s">
+      <c r="C63" s="22" t="s">
         <v>218</v>
       </c>
-      <c r="D63" s="23">
+      <c r="D63" s="22">
         <v>4</v>
       </c>
-      <c r="E63" s="24" t="s">
+      <c r="E63" s="23" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A64" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B64" s="23" t="s">
+    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B64" s="22" t="s">
         <v>215</v>
       </c>
-      <c r="C64" s="23" t="s">
+      <c r="C64" s="22" t="s">
         <v>219</v>
       </c>
-      <c r="D64" s="23">
+      <c r="D64" s="22">
         <v>4</v>
       </c>
-      <c r="E64" s="24" t="s">
+      <c r="E64" s="23" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A65" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B65" s="23" t="s">
+    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B65" s="22" t="s">
         <v>215</v>
       </c>
-      <c r="C65" s="23" t="s">
+      <c r="C65" s="22" t="s">
         <v>220</v>
       </c>
-      <c r="D65" s="23">
+      <c r="D65" s="22">
         <v>4</v>
       </c>
-      <c r="E65" s="24" t="s">
+      <c r="E65" s="23" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A66" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B66" s="23" t="s">
+    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B66" s="22" t="s">
         <v>215</v>
       </c>
-      <c r="C66" s="23" t="s">
+      <c r="C66" s="22" t="s">
         <v>221</v>
       </c>
-      <c r="D66" s="23">
+      <c r="D66" s="22">
         <v>4</v>
       </c>
-      <c r="E66" s="24" t="s">
+      <c r="E66" s="23" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A67" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B67" s="23" t="s">
+    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B67" s="22" t="s">
         <v>215</v>
       </c>
-      <c r="C67" s="23" t="s">
+      <c r="C67" s="22" t="s">
         <v>222</v>
       </c>
-      <c r="D67" s="23">
+      <c r="D67" s="22">
         <v>4</v>
       </c>
-      <c r="E67" s="24" t="s">
+      <c r="E67" s="23" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A68" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B68" s="23" t="s">
+    <row r="68" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B68" s="22" t="s">
         <v>215</v>
       </c>
-      <c r="C68" s="23" t="s">
+      <c r="C68" s="22" t="s">
         <v>223</v>
       </c>
-      <c r="D68" s="23">
+      <c r="D68" s="22">
         <v>4</v>
       </c>
-      <c r="E68" s="24" t="s">
+      <c r="E68" s="23" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A69" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B69" s="23" t="s">
+    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B69" s="22" t="s">
         <v>215</v>
       </c>
-      <c r="C69" s="23" t="s">
+      <c r="C69" s="22" t="s">
         <v>224</v>
       </c>
-      <c r="D69" s="23">
+      <c r="D69" s="22">
         <v>4</v>
       </c>
-      <c r="E69" s="24" t="s">
+      <c r="E69" s="23" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A70" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B70" s="23" t="s">
+    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B70" s="22" t="s">
         <v>215</v>
       </c>
-      <c r="C70" s="23" t="s">
+      <c r="C70" s="22" t="s">
         <v>225</v>
       </c>
-      <c r="D70" s="23">
+      <c r="D70" s="22">
         <v>4</v>
       </c>
-      <c r="E70" s="24" t="s">
+      <c r="E70" s="23" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A71" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B71" s="23" t="s">
+    <row r="71" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B71" s="22" t="s">
         <v>215</v>
       </c>
-      <c r="C71" s="23" t="s">
+      <c r="C71" s="22" t="s">
         <v>226</v>
       </c>
-      <c r="D71" s="23">
+      <c r="D71" s="22">
         <v>4</v>
       </c>
-      <c r="E71" s="24" t="s">
+      <c r="E71" s="23" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A72" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B72" s="23" t="s">
+    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B72" s="22" t="s">
         <v>215</v>
       </c>
-      <c r="C72" s="23" t="s">
+      <c r="C72" s="22" t="s">
         <v>227</v>
       </c>
-      <c r="D72" s="23">
+      <c r="D72" s="22">
         <v>4</v>
       </c>
-      <c r="E72" s="24" t="s">
+      <c r="E72" s="23" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A73" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B73" s="23" t="s">
+    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B73" s="22" t="s">
         <v>228</v>
       </c>
-      <c r="C73" s="23" t="s">
+      <c r="C73" s="22" t="s">
         <v>229</v>
       </c>
-      <c r="D73" s="23">
+      <c r="D73" s="22">
         <v>5</v>
       </c>
-      <c r="E73" s="24" t="s">
+      <c r="E73" s="23" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A74" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B74" s="23" t="s">
+    <row r="74" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B74" s="22" t="s">
         <v>228</v>
       </c>
-      <c r="C74" s="23" t="s">
+      <c r="C74" s="22" t="s">
         <v>231</v>
       </c>
-      <c r="D74" s="23">
+      <c r="D74" s="22">
         <v>5</v>
       </c>
-      <c r="E74" s="24" t="s">
+      <c r="E74" s="23" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A75" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B75" s="23" t="s">
+    <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B75" s="22" t="s">
         <v>228</v>
       </c>
-      <c r="C75" s="23" t="s">
+      <c r="C75" s="22" t="s">
         <v>232</v>
       </c>
-      <c r="D75" s="23">
+      <c r="D75" s="22">
         <v>5</v>
       </c>
-      <c r="E75" s="24" t="s">
+      <c r="E75" s="23" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A76" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B76" s="23" t="s">
+    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B76" s="22" t="s">
         <v>228</v>
       </c>
-      <c r="C76" s="23" t="s">
+      <c r="C76" s="22" t="s">
         <v>233</v>
       </c>
-      <c r="D76" s="23">
+      <c r="D76" s="22">
         <v>5</v>
       </c>
-      <c r="E76" s="24" t="s">
+      <c r="E76" s="23" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A77" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B77" s="23" t="s">
+    <row r="77" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B77" s="22" t="s">
         <v>228</v>
       </c>
-      <c r="C77" s="23" t="s">
+      <c r="C77" s="22" t="s">
         <v>234</v>
       </c>
-      <c r="D77" s="23">
+      <c r="D77" s="22">
         <v>5</v>
       </c>
-      <c r="E77" s="24" t="s">
+      <c r="E77" s="23" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A78" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B78" s="23" t="s">
+    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B78" s="22" t="s">
         <v>228</v>
       </c>
-      <c r="C78" s="23" t="s">
+      <c r="C78" s="22" t="s">
         <v>235</v>
       </c>
-      <c r="D78" s="23">
+      <c r="D78" s="22">
         <v>5</v>
       </c>
-      <c r="E78" s="24" t="s">
+      <c r="E78" s="23" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A79" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B79" s="23" t="s">
+    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B79" s="22" t="s">
         <v>228</v>
       </c>
-      <c r="C79" s="23" t="s">
+      <c r="C79" s="22" t="s">
         <v>236</v>
       </c>
-      <c r="D79" s="23">
+      <c r="D79" s="22">
         <v>5</v>
       </c>
-      <c r="E79" s="24" t="s">
+      <c r="E79" s="23" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A80" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B80" s="23" t="s">
+    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B80" s="22" t="s">
         <v>228</v>
       </c>
-      <c r="C80" s="23" t="s">
+      <c r="C80" s="22" t="s">
         <v>237</v>
       </c>
-      <c r="D80" s="23">
+      <c r="D80" s="22">
         <v>5</v>
       </c>
-      <c r="E80" s="24" t="s">
+      <c r="E80" s="23" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A81" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B81" s="23" t="s">
+    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B81" s="22" t="s">
         <v>228</v>
       </c>
-      <c r="C81" s="23" t="s">
+      <c r="C81" s="22" t="s">
         <v>238</v>
       </c>
-      <c r="D81" s="23">
+      <c r="D81" s="22">
         <v>5</v>
       </c>
-      <c r="E81" s="24" t="s">
+      <c r="E81" s="23" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A82" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B82" s="23" t="s">
+    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B82" s="22" t="s">
         <v>239</v>
       </c>
-      <c r="C82" s="23" t="s">
+      <c r="C82" s="22" t="s">
         <v>240</v>
       </c>
-      <c r="D82" s="23">
+      <c r="D82" s="22">
         <v>6</v>
       </c>
-      <c r="E82" s="24" t="s">
+      <c r="E82" s="23" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A83" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B83" s="23" t="s">
+    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B83" s="22" t="s">
         <v>239</v>
       </c>
-      <c r="C83" s="23" t="s">
+      <c r="C83" s="22" t="s">
         <v>242</v>
       </c>
-      <c r="D83" s="23">
+      <c r="D83" s="22">
         <v>6</v>
       </c>
-      <c r="E83" s="24" t="s">
+      <c r="E83" s="23" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A84" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B84" s="23" t="s">
+    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B84" s="22" t="s">
         <v>239</v>
       </c>
-      <c r="C84" s="23" t="s">
+      <c r="C84" s="22" t="s">
         <v>243</v>
       </c>
-      <c r="D84" s="23">
+      <c r="D84" s="22">
         <v>6</v>
       </c>
-      <c r="E84" s="24" t="s">
+      <c r="E84" s="23" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A85" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B85" s="23" t="s">
+    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B85" s="22" t="s">
         <v>239</v>
       </c>
-      <c r="C85" s="23" t="s">
+      <c r="C85" s="22" t="s">
         <v>244</v>
       </c>
-      <c r="D85" s="23">
+      <c r="D85" s="22">
         <v>6</v>
       </c>
-      <c r="E85" s="24" t="s">
+      <c r="E85" s="23" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A86" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B86" s="23" t="s">
+    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B86" s="22" t="s">
         <v>239</v>
       </c>
-      <c r="C86" s="23" t="s">
+      <c r="C86" s="22" t="s">
         <v>245</v>
       </c>
-      <c r="D86" s="23">
+      <c r="D86" s="22">
         <v>6</v>
       </c>
-      <c r="E86" s="24" t="s">
+      <c r="E86" s="23" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A87" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B87" s="23" t="s">
+    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B87" s="22" t="s">
         <v>239</v>
       </c>
-      <c r="C87" s="23" t="s">
+      <c r="C87" s="22" t="s">
         <v>246</v>
       </c>
-      <c r="D87" s="23">
+      <c r="D87" s="22">
         <v>6</v>
       </c>
-      <c r="E87" s="24" t="s">
+      <c r="E87" s="23" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A88" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B88" s="23" t="s">
+    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B88" s="22" t="s">
         <v>239</v>
       </c>
-      <c r="C88" s="23" t="s">
+      <c r="C88" s="22" t="s">
         <v>247</v>
       </c>
-      <c r="D88" s="23">
+      <c r="D88" s="22">
         <v>6</v>
       </c>
-      <c r="E88" s="24" t="s">
+      <c r="E88" s="23" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A89" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B89" s="23" t="s">
+    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B89" s="22" t="s">
         <v>239</v>
       </c>
-      <c r="C89" s="23" t="s">
+      <c r="C89" s="22" t="s">
         <v>248</v>
       </c>
-      <c r="D89" s="23">
+      <c r="D89" s="22">
         <v>6</v>
       </c>
-      <c r="E89" s="24" t="s">
+      <c r="E89" s="23" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A90" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B90" s="23" t="s">
+    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B90" s="22" t="s">
         <v>239</v>
       </c>
-      <c r="C90" s="23" t="s">
+      <c r="C90" s="22" t="s">
         <v>249</v>
       </c>
-      <c r="D90" s="23">
+      <c r="D90" s="22">
         <v>6</v>
       </c>
-      <c r="E90" s="24" t="s">
+      <c r="E90" s="23" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A91" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B91" s="23" t="s">
+    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B91" s="22" t="s">
         <v>239</v>
       </c>
-      <c r="C91" s="23" t="s">
+      <c r="C91" s="22" t="s">
         <v>250</v>
       </c>
-      <c r="D91" s="23">
+      <c r="D91" s="22">
         <v>6</v>
       </c>
-      <c r="E91" s="24" t="s">
+      <c r="E91" s="23" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A92" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B92" s="23" t="s">
+    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B92" s="22" t="s">
         <v>239</v>
       </c>
-      <c r="C92" s="23" t="s">
+      <c r="C92" s="22" t="s">
         <v>251</v>
       </c>
-      <c r="D92" s="23">
+      <c r="D92" s="22">
         <v>6</v>
       </c>
-      <c r="E92" s="24" t="s">
+      <c r="E92" s="23" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A93" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B93" s="23" t="s">
+    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B93" s="22" t="s">
         <v>239</v>
       </c>
-      <c r="C93" s="23" t="s">
+      <c r="C93" s="22" t="s">
         <v>252</v>
       </c>
-      <c r="D93" s="23">
+      <c r="D93" s="22">
         <v>6</v>
       </c>
-      <c r="E93" s="24" t="s">
+      <c r="E93" s="23" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A94" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B94" s="23" t="s">
+    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B94" s="22" t="s">
         <v>239</v>
       </c>
-      <c r="C94" s="23" t="s">
+      <c r="C94" s="22" t="s">
         <v>253</v>
       </c>
-      <c r="D94" s="23">
+      <c r="D94" s="22">
         <v>6</v>
       </c>
-      <c r="E94" s="24" t="s">
+      <c r="E94" s="23" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A95" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B95" s="23" t="s">
+    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B95" s="22" t="s">
         <v>254</v>
       </c>
-      <c r="C95" s="23" t="s">
+      <c r="C95" s="22" t="s">
         <v>255</v>
       </c>
-      <c r="D95" s="23">
+      <c r="D95" s="22">
         <v>7</v>
       </c>
-      <c r="E95" s="24" t="s">
+      <c r="E95" s="23" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A96" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B96" s="23" t="s">
+    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B96" s="22" t="s">
         <v>254</v>
       </c>
-      <c r="C96" s="23" t="s">
+      <c r="C96" s="22" t="s">
         <v>257</v>
       </c>
-      <c r="D96" s="23">
+      <c r="D96" s="22">
         <v>7</v>
       </c>
-      <c r="E96" s="24" t="s">
+      <c r="E96" s="23" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A97" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B97" s="23" t="s">
+    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B97" s="22" t="s">
         <v>254</v>
       </c>
-      <c r="C97" s="23" t="s">
+      <c r="C97" s="22" t="s">
         <v>258</v>
       </c>
-      <c r="D97" s="23">
+      <c r="D97" s="22">
         <v>7</v>
       </c>
-      <c r="E97" s="24" t="s">
+      <c r="E97" s="23" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A98" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B98" s="23" t="s">
+    <row r="98" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B98" s="22" t="s">
         <v>254</v>
       </c>
-      <c r="C98" s="23" t="s">
+      <c r="C98" s="22" t="s">
         <v>259</v>
       </c>
-      <c r="D98" s="23">
+      <c r="D98" s="22">
         <v>7</v>
       </c>
-      <c r="E98" s="24" t="s">
+      <c r="E98" s="23" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A99" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B99" s="23" t="s">
+    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B99" s="22" t="s">
         <v>254</v>
       </c>
-      <c r="C99" s="23" t="s">
+      <c r="C99" s="22" t="s">
         <v>260</v>
       </c>
-      <c r="D99" s="23">
+      <c r="D99" s="22">
         <v>7</v>
       </c>
-      <c r="E99" s="24" t="s">
+      <c r="E99" s="23" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A100" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B100" s="23" t="s">
+    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B100" s="22" t="s">
         <v>254</v>
       </c>
-      <c r="C100" s="23" t="s">
+      <c r="C100" s="22" t="s">
         <v>261</v>
       </c>
-      <c r="D100" s="23">
+      <c r="D100" s="22">
         <v>7</v>
       </c>
-      <c r="E100" s="24" t="s">
+      <c r="E100" s="23" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A101" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B101" s="23" t="s">
+    <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B101" s="22" t="s">
         <v>254</v>
       </c>
-      <c r="C101" s="23" t="s">
+      <c r="C101" s="22" t="s">
         <v>262</v>
       </c>
-      <c r="D101" s="23">
+      <c r="D101" s="22">
         <v>7</v>
       </c>
-      <c r="E101" s="24" t="s">
+      <c r="E101" s="23" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A102" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B102" s="23" t="s">
+    <row r="102" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B102" s="22" t="s">
         <v>254</v>
       </c>
-      <c r="C102" s="23" t="s">
+      <c r="C102" s="22" t="s">
         <v>263</v>
       </c>
-      <c r="D102" s="23">
+      <c r="D102" s="22">
         <v>7</v>
       </c>
-      <c r="E102" s="24" t="s">
+      <c r="E102" s="23" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A103" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B103" s="23" t="s">
+    <row r="103" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B103" s="22" t="s">
         <v>264</v>
       </c>
-      <c r="C103" s="23" t="s">
+      <c r="C103" s="22" t="s">
         <v>265</v>
       </c>
-      <c r="D103" s="23">
+      <c r="D103" s="22">
         <v>8</v>
       </c>
-      <c r="E103" s="24" t="s">
+      <c r="E103" s="23" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A104" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B104" s="23" t="s">
+    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B104" s="22" t="s">
         <v>264</v>
       </c>
-      <c r="C104" s="23" t="s">
+      <c r="C104" s="22" t="s">
         <v>267</v>
       </c>
-      <c r="D104" s="23">
+      <c r="D104" s="22">
         <v>8</v>
       </c>
-      <c r="E104" s="24" t="s">
+      <c r="E104" s="23" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A105" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B105" s="23" t="s">
+    <row r="105" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B105" s="22" t="s">
         <v>264</v>
       </c>
-      <c r="C105" s="23" t="s">
+      <c r="C105" s="22" t="s">
         <v>268</v>
       </c>
-      <c r="D105" s="23">
+      <c r="D105" s="22">
         <v>8</v>
       </c>
-      <c r="E105" s="24" t="s">
+      <c r="E105" s="23" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A106" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B106" s="23" t="s">
+    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B106" s="22" t="s">
         <v>264</v>
       </c>
-      <c r="C106" s="23" t="s">
+      <c r="C106" s="22" t="s">
         <v>269</v>
       </c>
-      <c r="D106" s="23">
+      <c r="D106" s="22">
         <v>8</v>
       </c>
-      <c r="E106" s="24" t="s">
+      <c r="E106" s="23" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A107" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B107" s="23" t="s">
+    <row r="107" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B107" s="22" t="s">
         <v>264</v>
       </c>
-      <c r="C107" s="23" t="s">
+      <c r="C107" s="22" t="s">
         <v>270</v>
       </c>
-      <c r="D107" s="23">
+      <c r="D107" s="22">
         <v>8</v>
       </c>
-      <c r="E107" s="24" t="s">
+      <c r="E107" s="23" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A108" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B108" s="23" t="s">
+    <row r="108" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B108" s="22" t="s">
         <v>264</v>
       </c>
-      <c r="C108" s="23" t="s">
+      <c r="C108" s="22" t="s">
         <v>271</v>
       </c>
-      <c r="D108" s="23">
+      <c r="D108" s="22">
         <v>8</v>
       </c>
-      <c r="E108" s="24" t="s">
+      <c r="E108" s="23" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A109" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B109" s="23" t="s">
+    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B109" s="22" t="s">
         <v>264</v>
       </c>
-      <c r="C109" s="23" t="s">
+      <c r="C109" s="22" t="s">
         <v>272</v>
       </c>
-      <c r="D109" s="23">
+      <c r="D109" s="22">
         <v>8</v>
       </c>
-      <c r="E109" s="24" t="s">
+      <c r="E109" s="23" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A110" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B110" s="23" t="s">
+    <row r="110" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B110" s="22" t="s">
         <v>264</v>
       </c>
-      <c r="C110" s="23" t="s">
+      <c r="C110" s="22" t="s">
         <v>273</v>
       </c>
-      <c r="D110" s="23">
+      <c r="D110" s="22">
         <v>8</v>
       </c>
-      <c r="E110" s="24" t="s">
+      <c r="E110" s="23" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A111" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B111" s="23" t="s">
+    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A111" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B111" s="22" t="s">
         <v>264</v>
       </c>
-      <c r="C111" s="23" t="s">
+      <c r="C111" s="22" t="s">
         <v>274</v>
       </c>
-      <c r="D111" s="23">
+      <c r="D111" s="22">
         <v>8</v>
       </c>
-      <c r="E111" s="24" t="s">
+      <c r="E111" s="23" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A112" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B112" s="23" t="s">
+    <row r="112" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B112" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="C112" s="23" t="s">
+      <c r="C112" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="D112" s="23">
+      <c r="D112" s="22">
         <v>9</v>
       </c>
-      <c r="E112" s="24" t="s">
+      <c r="E112" s="23" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A113" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B113" s="23" t="s">
+    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B113" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="C113" s="23" t="s">
+      <c r="C113" s="22" t="s">
         <v>276</v>
       </c>
-      <c r="D113" s="23">
+      <c r="D113" s="22">
         <v>9</v>
       </c>
-      <c r="E113" s="24" t="s">
+      <c r="E113" s="23" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A114" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B114" s="23" t="s">
+    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B114" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="C114" s="23" t="s">
+      <c r="C114" s="22" t="s">
         <v>278</v>
       </c>
-      <c r="D114" s="23">
+      <c r="D114" s="22">
         <v>9</v>
       </c>
-      <c r="E114" s="24" t="s">
+      <c r="E114" s="23" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A115" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B115" s="23" t="s">
+    <row r="115" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B115" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="C115" s="23" t="s">
+      <c r="C115" s="22" t="s">
         <v>279</v>
       </c>
-      <c r="D115" s="23">
+      <c r="D115" s="22">
         <v>9</v>
       </c>
-      <c r="E115" s="24" t="s">
+      <c r="E115" s="23" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A116" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B116" s="23" t="s">
+    <row r="116" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B116" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="C116" s="23" t="s">
+      <c r="C116" s="22" t="s">
         <v>280</v>
       </c>
-      <c r="D116" s="23">
+      <c r="D116" s="22">
         <v>9</v>
       </c>
-      <c r="E116" s="24" t="s">
+      <c r="E116" s="23" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A117" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B117" s="23" t="s">
+    <row r="117" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B117" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="C117" s="23" t="s">
+      <c r="C117" s="22" t="s">
         <v>281</v>
       </c>
-      <c r="D117" s="23">
+      <c r="D117" s="22">
         <v>9</v>
       </c>
-      <c r="E117" s="24" t="s">
+      <c r="E117" s="23" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A118" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B118" s="23" t="s">
+    <row r="118" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B118" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="C118" s="23" t="s">
+      <c r="C118" s="22" t="s">
         <v>282</v>
       </c>
-      <c r="D118" s="23">
+      <c r="D118" s="22">
         <v>9</v>
       </c>
-      <c r="E118" s="24" t="s">
+      <c r="E118" s="23" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A119" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B119" s="23" t="s">
+    <row r="119" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A119" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B119" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="C119" s="23" t="s">
+      <c r="C119" s="22" t="s">
         <v>283</v>
       </c>
-      <c r="D119" s="23">
+      <c r="D119" s="22">
         <v>9</v>
       </c>
-      <c r="E119" s="24" t="s">
+      <c r="E119" s="23" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A120" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B120" s="23" t="s">
+    <row r="120" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B120" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="C120" s="23" t="s">
+      <c r="C120" s="22" t="s">
         <v>284</v>
       </c>
-      <c r="D120" s="23">
+      <c r="D120" s="22">
         <v>9</v>
       </c>
-      <c r="E120" s="24" t="s">
+      <c r="E120" s="23" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A121" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B121" s="23" t="s">
+    <row r="121" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B121" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="C121" s="23" t="s">
+      <c r="C121" s="22" t="s">
         <v>285</v>
       </c>
-      <c r="D121" s="23">
+      <c r="D121" s="22">
         <v>9</v>
       </c>
-      <c r="E121" s="24" t="s">
+      <c r="E121" s="23" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A122" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B122" s="23" t="s">
+    <row r="122" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B122" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="C122" s="23" t="s">
+      <c r="C122" s="22" t="s">
         <v>287</v>
       </c>
-      <c r="D122" s="23">
+      <c r="D122" s="22">
         <v>9</v>
       </c>
-      <c r="E122" s="24" t="s">
+      <c r="E122" s="23" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A123" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B123" s="23" t="s">
+    <row r="123" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A123" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B123" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="C123" s="23" t="s">
+      <c r="C123" s="22" t="s">
         <v>288</v>
       </c>
-      <c r="D123" s="23">
+      <c r="D123" s="22">
         <v>9</v>
       </c>
-      <c r="E123" s="24" t="s">
+      <c r="E123" s="23" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A124" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B124" s="23" t="s">
+    <row r="124" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A124" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B124" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="C124" s="23" t="s">
+      <c r="C124" s="22" t="s">
         <v>289</v>
       </c>
-      <c r="D124" s="23">
+      <c r="D124" s="22">
         <v>9</v>
       </c>
-      <c r="E124" s="24" t="s">
+      <c r="E124" s="23" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A125" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B125" s="23" t="s">
+    <row r="125" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A125" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B125" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="C125" s="23" t="s">
+      <c r="C125" s="22" t="s">
         <v>290</v>
       </c>
-      <c r="D125" s="23">
+      <c r="D125" s="22">
         <v>9</v>
       </c>
-      <c r="E125" s="24" t="s">
+      <c r="E125" s="23" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A126" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B126" s="23" t="s">
+    <row r="126" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A126" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B126" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="C126" s="23" t="s">
+      <c r="C126" s="22" t="s">
         <v>291</v>
       </c>
-      <c r="D126" s="23">
+      <c r="D126" s="22">
         <v>9</v>
       </c>
-      <c r="E126" s="24" t="s">
+      <c r="E126" s="23" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A127" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B127" s="23" t="s">
+    <row r="127" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A127" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B127" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="C127" s="23" t="s">
+      <c r="C127" s="22" t="s">
         <v>292</v>
       </c>
-      <c r="D127" s="23">
+      <c r="D127" s="22">
         <v>9</v>
       </c>
-      <c r="E127" s="24" t="s">
+      <c r="E127" s="23" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A128" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B128" s="23" t="s">
+    <row r="128" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A128" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B128" s="22" t="s">
         <v>293</v>
       </c>
-      <c r="C128" s="23" t="s">
+      <c r="C128" s="22" t="s">
         <v>294</v>
       </c>
-      <c r="D128" s="23">
+      <c r="D128" s="22">
         <v>10</v>
       </c>
-      <c r="E128" s="24" t="s">
+      <c r="E128" s="23" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A129" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B129" s="23" t="s">
+    <row r="129" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A129" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B129" s="22" t="s">
         <v>293</v>
       </c>
-      <c r="C129" s="23" t="s">
+      <c r="C129" s="22" t="s">
         <v>296</v>
       </c>
-      <c r="D129" s="23">
+      <c r="D129" s="22">
         <v>10</v>
       </c>
-      <c r="E129" s="24" t="s">
+      <c r="E129" s="23" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A130" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B130" s="23" t="s">
+    <row r="130" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A130" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B130" s="22" t="s">
         <v>293</v>
       </c>
-      <c r="C130" s="23" t="s">
+      <c r="C130" s="22" t="s">
         <v>297</v>
       </c>
-      <c r="D130" s="23">
+      <c r="D130" s="22">
         <v>10</v>
       </c>
-      <c r="E130" s="24" t="s">
+      <c r="E130" s="23" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A131" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B131" s="23" t="s">
+    <row r="131" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A131" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B131" s="22" t="s">
         <v>293</v>
       </c>
-      <c r="C131" s="23" t="s">
+      <c r="C131" s="22" t="s">
         <v>298</v>
       </c>
-      <c r="D131" s="23">
+      <c r="D131" s="22">
         <v>10</v>
       </c>
-      <c r="E131" s="24" t="s">
+      <c r="E131" s="23" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A132" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B132" s="23" t="s">
+    <row r="132" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A132" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B132" s="22" t="s">
         <v>293</v>
       </c>
-      <c r="C132" s="23" t="s">
+      <c r="C132" s="22" t="s">
         <v>299</v>
       </c>
-      <c r="D132" s="23">
+      <c r="D132" s="22">
         <v>10</v>
       </c>
-      <c r="E132" s="24" t="s">
+      <c r="E132" s="23" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A133" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B133" s="23" t="s">
+    <row r="133" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A133" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B133" s="22" t="s">
         <v>293</v>
       </c>
-      <c r="C133" s="23" t="s">
+      <c r="C133" s="22" t="s">
         <v>300</v>
       </c>
-      <c r="D133" s="23">
+      <c r="D133" s="22">
         <v>10</v>
       </c>
-      <c r="E133" s="24" t="s">
+      <c r="E133" s="23" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A134" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B134" s="23" t="s">
+    <row r="134" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A134" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B134" s="22" t="s">
         <v>293</v>
       </c>
-      <c r="C134" s="23" t="s">
+      <c r="C134" s="22" t="s">
         <v>301</v>
       </c>
-      <c r="D134" s="23">
+      <c r="D134" s="22">
         <v>10</v>
       </c>
-      <c r="E134" s="24" t="s">
+      <c r="E134" s="23" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A135" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B135" s="23" t="s">
+    <row r="135" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A135" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B135" s="22" t="s">
         <v>293</v>
       </c>
-      <c r="C135" s="23" t="s">
+      <c r="C135" s="22" t="s">
         <v>302</v>
       </c>
-      <c r="D135" s="23">
+      <c r="D135" s="22">
         <v>10</v>
       </c>
-      <c r="E135" s="24" t="s">
+      <c r="E135" s="23" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A136" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B136" s="23" t="s">
+    <row r="136" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A136" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B136" s="22" t="s">
         <v>293</v>
       </c>
-      <c r="C136" s="23" t="s">
+      <c r="C136" s="22" t="s">
         <v>303</v>
       </c>
-      <c r="D136" s="23">
+      <c r="D136" s="22">
         <v>10</v>
       </c>
-      <c r="E136" s="24" t="s">
+      <c r="E136" s="23" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A137" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B137" s="23" t="s">
+    <row r="137" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A137" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B137" s="22" t="s">
         <v>293</v>
       </c>
-      <c r="C137" s="23" t="s">
+      <c r="C137" s="22" t="s">
         <v>304</v>
       </c>
-      <c r="D137" s="23">
+      <c r="D137" s="22">
         <v>10</v>
       </c>
-      <c r="E137" s="24" t="s">
+      <c r="E137" s="23" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A138" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B138" s="23" t="s">
+    <row r="138" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A138" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B138" s="22" t="s">
         <v>293</v>
       </c>
-      <c r="C138" s="23" t="s">
+      <c r="C138" s="22" t="s">
         <v>305</v>
       </c>
-      <c r="D138" s="23">
+      <c r="D138" s="22">
         <v>10</v>
       </c>
-      <c r="E138" s="24" t="s">
+      <c r="E138" s="23" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A139" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B139" s="23" t="s">
+    <row r="139" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A139" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B139" s="22" t="s">
         <v>293</v>
       </c>
-      <c r="C139" s="23" t="s">
+      <c r="C139" s="22" t="s">
         <v>306</v>
       </c>
-      <c r="D139" s="23">
+      <c r="D139" s="22">
         <v>10</v>
       </c>
-      <c r="E139" s="24" t="s">
+      <c r="E139" s="23" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A140" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B140" s="23" t="s">
+    <row r="140" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A140" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B140" s="22" t="s">
         <v>293</v>
       </c>
-      <c r="C140" s="23" t="s">
+      <c r="C140" s="22" t="s">
         <v>307</v>
       </c>
-      <c r="D140" s="23">
+      <c r="D140" s="22">
         <v>10</v>
       </c>
-      <c r="E140" s="24" t="s">
+      <c r="E140" s="23" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A141" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B141" s="23" t="s">
+    <row r="141" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A141" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B141" s="22" t="s">
         <v>293</v>
       </c>
-      <c r="C141" s="23" t="s">
+      <c r="C141" s="22" t="s">
         <v>308</v>
       </c>
-      <c r="D141" s="23">
+      <c r="D141" s="22">
         <v>10</v>
       </c>
-      <c r="E141" s="24" t="s">
+      <c r="E141" s="23" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A142" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B142" s="23" t="s">
+    <row r="142" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A142" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B142" s="22" t="s">
         <v>293</v>
       </c>
-      <c r="C142" s="23" t="s">
+      <c r="C142" s="22" t="s">
         <v>309</v>
       </c>
-      <c r="D142" s="23">
+      <c r="D142" s="22">
         <v>10</v>
       </c>
-      <c r="E142" s="24" t="s">
+      <c r="E142" s="23" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A143" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B143" s="23" t="s">
+    <row r="143" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A143" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B143" s="22" t="s">
         <v>293</v>
       </c>
-      <c r="C143" s="23" t="s">
+      <c r="C143" s="22" t="s">
         <v>310</v>
       </c>
-      <c r="D143" s="23">
+      <c r="D143" s="22">
         <v>10</v>
       </c>
-      <c r="E143" s="24" t="s">
+      <c r="E143" s="23" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A144" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B144" s="23" t="s">
+    <row r="144" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A144" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B144" s="22" t="s">
         <v>293</v>
       </c>
-      <c r="C144" s="23" t="s">
+      <c r="C144" s="22" t="s">
         <v>311</v>
       </c>
-      <c r="D144" s="23">
+      <c r="D144" s="22">
         <v>10</v>
       </c>
-      <c r="E144" s="24" t="s">
+      <c r="E144" s="23" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A145" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B145" s="23" t="s">
+    <row r="145" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A145" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B145" s="22" t="s">
         <v>293</v>
       </c>
-      <c r="C145" s="23" t="s">
+      <c r="C145" s="22" t="s">
         <v>312</v>
       </c>
-      <c r="D145" s="23">
+      <c r="D145" s="22">
         <v>10</v>
       </c>
-      <c r="E145" s="24" t="s">
+      <c r="E145" s="23" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A146" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B146" s="23" t="s">
+    <row r="146" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A146" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B146" s="22" t="s">
         <v>293</v>
       </c>
-      <c r="C146" s="23" t="s">
+      <c r="C146" s="22" t="s">
         <v>313</v>
       </c>
-      <c r="D146" s="23">
+      <c r="D146" s="22">
         <v>10</v>
       </c>
-      <c r="E146" s="24" t="s">
+      <c r="E146" s="23" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A147" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B147" s="23" t="s">
+    <row r="147" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A147" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B147" s="22" t="s">
         <v>293</v>
       </c>
-      <c r="C147" s="23" t="s">
+      <c r="C147" s="22" t="s">
         <v>314</v>
       </c>
-      <c r="D147" s="23">
+      <c r="D147" s="22">
         <v>10</v>
       </c>
-      <c r="E147" s="24" t="s">
+      <c r="E147" s="23" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A148" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B148" s="23" t="s">
+    <row r="148" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A148" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B148" s="22" t="s">
         <v>293</v>
       </c>
-      <c r="C148" s="23" t="s">
+      <c r="C148" s="22" t="s">
         <v>315</v>
       </c>
-      <c r="D148" s="23">
+      <c r="D148" s="22">
         <v>10</v>
       </c>
-      <c r="E148" s="24" t="s">
+      <c r="E148" s="23" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A149" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B149" s="23" t="s">
+    <row r="149" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A149" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B149" s="22" t="s">
         <v>293</v>
       </c>
-      <c r="C149" s="23" t="s">
+      <c r="C149" s="22" t="s">
         <v>316</v>
       </c>
-      <c r="D149" s="23">
+      <c r="D149" s="22">
         <v>10</v>
       </c>
-      <c r="E149" s="24" t="s">
+      <c r="E149" s="23" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A150" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B150" s="23" t="s">
+    <row r="150" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A150" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B150" s="22" t="s">
         <v>293</v>
       </c>
-      <c r="C150" s="23" t="s">
+      <c r="C150" s="22" t="s">
         <v>317</v>
       </c>
-      <c r="D150" s="23">
+      <c r="D150" s="22">
         <v>10</v>
       </c>
-      <c r="E150" s="24" t="s">
+      <c r="E150" s="23" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A151" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B151" s="23" t="s">
+    <row r="151" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A151" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B151" s="22" t="s">
         <v>293</v>
       </c>
-      <c r="C151" s="23" t="s">
+      <c r="C151" s="22" t="s">
         <v>318</v>
       </c>
-      <c r="D151" s="23">
+      <c r="D151" s="22">
         <v>10</v>
       </c>
-      <c r="E151" s="24" t="s">
+      <c r="E151" s="23" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A152" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B152" s="23" t="s">
+    <row r="152" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A152" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B152" s="22" t="s">
         <v>293</v>
       </c>
-      <c r="C152" s="23" t="s">
+      <c r="C152" s="22" t="s">
         <v>319</v>
       </c>
-      <c r="D152" s="23">
+      <c r="D152" s="22">
         <v>10</v>
       </c>
-      <c r="E152" s="24" t="s">
+      <c r="E152" s="23" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A153" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B153" s="23" t="s">
+    <row r="153" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A153" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B153" s="22" t="s">
         <v>320</v>
       </c>
-      <c r="C153" s="23" t="s">
+      <c r="C153" s="22" t="s">
         <v>321</v>
       </c>
-      <c r="D153" s="23">
+      <c r="D153" s="22">
         <v>11</v>
       </c>
-      <c r="E153" s="24" t="s">
+      <c r="E153" s="23" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A154" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B154" s="23" t="s">
+    <row r="154" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A154" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B154" s="22" t="s">
         <v>320</v>
       </c>
-      <c r="C154" s="23" t="s">
+      <c r="C154" s="22" t="s">
         <v>323</v>
       </c>
-      <c r="D154" s="23">
+      <c r="D154" s="22">
         <v>11</v>
       </c>
-      <c r="E154" s="24" t="s">
+      <c r="E154" s="23" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A155" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B155" s="23" t="s">
+    <row r="155" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A155" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B155" s="22" t="s">
         <v>320</v>
       </c>
-      <c r="C155" s="23" t="s">
+      <c r="C155" s="22" t="s">
         <v>324</v>
       </c>
-      <c r="D155" s="23">
+      <c r="D155" s="22">
         <v>11</v>
       </c>
-      <c r="E155" s="24" t="s">
+      <c r="E155" s="23" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A156" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B156" s="23" t="s">
+    <row r="156" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A156" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B156" s="22" t="s">
         <v>320</v>
       </c>
-      <c r="C156" s="23" t="s">
+      <c r="C156" s="22" t="s">
         <v>325</v>
       </c>
-      <c r="D156" s="23">
+      <c r="D156" s="22">
         <v>11</v>
       </c>
-      <c r="E156" s="24" t="s">
+      <c r="E156" s="23" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A157" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B157" s="23" t="s">
+    <row r="157" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A157" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B157" s="22" t="s">
         <v>320</v>
       </c>
-      <c r="C157" s="23" t="s">
+      <c r="C157" s="22" t="s">
         <v>326</v>
       </c>
-      <c r="D157" s="23">
+      <c r="D157" s="22">
         <v>11</v>
       </c>
-      <c r="E157" s="24" t="s">
+      <c r="E157" s="23" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A158" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B158" s="23" t="s">
+    <row r="158" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A158" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B158" s="22" t="s">
         <v>320</v>
       </c>
-      <c r="C158" s="23" t="s">
+      <c r="C158" s="22" t="s">
         <v>327</v>
       </c>
-      <c r="D158" s="23">
+      <c r="D158" s="22">
         <v>11</v>
       </c>
-      <c r="E158" s="24" t="s">
+      <c r="E158" s="23" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A159" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B159" s="23" t="s">
+    <row r="159" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A159" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B159" s="22" t="s">
         <v>320</v>
       </c>
-      <c r="C159" s="23" t="s">
+      <c r="C159" s="22" t="s">
         <v>328</v>
       </c>
-      <c r="D159" s="23">
+      <c r="D159" s="22">
         <v>11</v>
       </c>
-      <c r="E159" s="24" t="s">
+      <c r="E159" s="23" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A160" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B160" s="23" t="s">
+    <row r="160" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A160" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B160" s="22" t="s">
         <v>320</v>
       </c>
-      <c r="C160" s="23" t="s">
+      <c r="C160" s="22" t="s">
         <v>329</v>
       </c>
-      <c r="D160" s="23">
+      <c r="D160" s="22">
         <v>11</v>
       </c>
-      <c r="E160" s="24" t="s">
+      <c r="E160" s="23" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A161" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B161" s="23" t="s">
+    <row r="161" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A161" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B161" s="22" t="s">
         <v>320</v>
       </c>
-      <c r="C161" s="23" t="s">
+      <c r="C161" s="22" t="s">
         <v>330</v>
       </c>
-      <c r="D161" s="23">
+      <c r="D161" s="22">
         <v>11</v>
       </c>
-      <c r="E161" s="24" t="s">
+      <c r="E161" s="23" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A162" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B162" s="23" t="s">
+    <row r="162" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A162" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B162" s="22" t="s">
         <v>320</v>
       </c>
-      <c r="C162" s="23" t="s">
+      <c r="C162" s="22" t="s">
         <v>331</v>
       </c>
-      <c r="D162" s="23">
+      <c r="D162" s="22">
         <v>11</v>
       </c>
-      <c r="E162" s="24" t="s">
+      <c r="E162" s="23" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A163" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B163" s="23" t="s">
+    <row r="163" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A163" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B163" s="22" t="s">
         <v>320</v>
       </c>
-      <c r="C163" s="23" t="s">
+      <c r="C163" s="22" t="s">
         <v>332</v>
       </c>
-      <c r="D163" s="23">
+      <c r="D163" s="22">
         <v>11</v>
       </c>
-      <c r="E163" s="24" t="s">
+      <c r="E163" s="23" t="s">
         <v>322</v>
       </c>
     </row>
@@ -6849,7 +7301,7 @@
       <c r="B179" s="8" t="s">
         <v>334</v>
       </c>
-      <c r="C179" s="25" t="s">
+      <c r="C179" s="24" t="s">
         <v>353</v>
       </c>
       <c r="D179" s="8">
@@ -6866,7 +7318,7 @@
       <c r="B180" s="8" t="s">
         <v>334</v>
       </c>
-      <c r="C180" s="26" t="s">
+      <c r="C180" s="25" t="s">
         <v>355</v>
       </c>
       <c r="D180" s="8">
@@ -6883,7 +7335,7 @@
       <c r="B181" s="8" t="s">
         <v>334</v>
       </c>
-      <c r="C181" s="26" t="s">
+      <c r="C181" s="25" t="s">
         <v>356</v>
       </c>
       <c r="D181" s="8">
@@ -6900,7 +7352,7 @@
       <c r="B182" s="8" t="s">
         <v>334</v>
       </c>
-      <c r="C182" s="25" t="s">
+      <c r="C182" s="24" t="s">
         <v>358</v>
       </c>
       <c r="D182" s="8">
@@ -7784,7 +8236,7 @@
       <c r="B234" s="8" t="s">
         <v>409</v>
       </c>
-      <c r="C234" s="26" t="s">
+      <c r="C234" s="25" t="s">
         <v>428</v>
       </c>
       <c r="D234" s="8">
@@ -7801,7 +8253,7 @@
       <c r="B235" s="8" t="s">
         <v>409</v>
       </c>
-      <c r="C235" s="25" t="s">
+      <c r="C235" s="24" t="s">
         <v>429</v>
       </c>
       <c r="D235" s="8">
@@ -7914,23 +8366,23 @@
       </c>
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A242" s="16" t="s">
+      <c r="A242" s="15" t="s">
         <v>333</v>
       </c>
-      <c r="B242" s="17" t="s">
+      <c r="B242" s="16" t="s">
         <v>409</v>
       </c>
-      <c r="C242" s="17" t="s">
+      <c r="C242" s="16" t="s">
         <v>439</v>
       </c>
-      <c r="D242" s="17">
+      <c r="D242" s="16">
         <v>3</v>
       </c>
-      <c r="E242" s="18" t="s">
+      <c r="E242" s="17" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" s="11" t="s">
         <v>440</v>
       </c>
@@ -7947,7 +8399,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" s="11" t="s">
         <v>440</v>
       </c>
@@ -7964,7 +8416,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" s="11" t="s">
         <v>440</v>
       </c>
@@ -7981,7 +8433,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" s="11" t="s">
         <v>440</v>
       </c>
@@ -7998,7 +8450,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" s="11" t="s">
         <v>440</v>
       </c>
@@ -8015,7 +8467,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" s="11" t="s">
         <v>440</v>
       </c>
@@ -8032,7 +8484,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" s="11" t="s">
         <v>440</v>
       </c>
@@ -8049,7 +8501,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" s="11" t="s">
         <v>440</v>
       </c>
@@ -8066,7 +8518,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" s="11" t="s">
         <v>440</v>
       </c>
@@ -8083,7 +8535,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" s="11" t="s">
         <v>440</v>
       </c>
@@ -8100,24 +8552,24 @@
         <v>461</v>
       </c>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A253" s="16" t="s">
+    <row r="253" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A253" s="15" t="s">
         <v>440</v>
       </c>
-      <c r="B253" s="17" t="s">
+      <c r="B253" s="16" t="s">
         <v>441</v>
       </c>
-      <c r="C253" s="17" t="s">
+      <c r="C253" s="16" t="s">
         <v>462</v>
       </c>
-      <c r="D253" s="17">
-        <v>1</v>
-      </c>
-      <c r="E253" s="18" t="s">
+      <c r="D253" s="16">
+        <v>1</v>
+      </c>
+      <c r="E253" s="17" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" s="11" t="s">
         <v>440</v>
       </c>
@@ -8134,7 +8586,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" s="11" t="s">
         <v>440</v>
       </c>
@@ -8151,7 +8603,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" s="11" t="s">
         <v>440</v>
       </c>
@@ -8168,7 +8620,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" s="11" t="s">
         <v>440</v>
       </c>
@@ -8185,7 +8637,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" s="11" t="s">
         <v>440</v>
       </c>
@@ -8202,7 +8654,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" s="11" t="s">
         <v>440</v>
       </c>
@@ -8219,7 +8671,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" s="11" t="s">
         <v>440</v>
       </c>
@@ -8236,7 +8688,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" s="11" t="s">
         <v>440</v>
       </c>
@@ -8253,7 +8705,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" s="11" t="s">
         <v>440</v>
       </c>
@@ -8270,7 +8722,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" s="11" t="s">
         <v>440</v>
       </c>
@@ -8287,7 +8739,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" s="11" t="s">
         <v>440</v>
       </c>
@@ -8304,7 +8756,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" s="11" t="s">
         <v>440</v>
       </c>
@@ -8321,7 +8773,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" s="11" t="s">
         <v>440</v>
       </c>
@@ -8338,7 +8790,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" s="11" t="s">
         <v>440</v>
       </c>
@@ -8355,7 +8807,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" s="11" t="s">
         <v>440</v>
       </c>
@@ -8372,7 +8824,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" s="11" t="s">
         <v>440</v>
       </c>
@@ -8389,7 +8841,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" s="11" t="s">
         <v>440</v>
       </c>
@@ -8406,7 +8858,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" s="11" t="s">
         <v>440</v>
       </c>
@@ -8423,7 +8875,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" s="11" t="s">
         <v>440</v>
       </c>
@@ -8440,7 +8892,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" s="11" t="s">
         <v>440</v>
       </c>
@@ -8457,7 +8909,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" s="11" t="s">
         <v>440</v>
       </c>
@@ -8474,7 +8926,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275" s="11" t="s">
         <v>440</v>
       </c>
